--- a/byn/BYN_JaDE_WBS.xlsx
+++ b/byn/BYN_JaDE_WBS.xlsx
@@ -844,7 +844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1023,6 +1023,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1388,7 +1389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:AC74"/>
+  <dimension ref="A2:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="16.09765625" customWidth="1" min="1" max="1"/>
@@ -3533,30 +3534,30 @@
         </is>
       </c>
       <c r="C58" s="53" t="n"/>
-      <c r="D58" s="102" t="n"/>
-      <c r="E58" s="103" t="n"/>
-      <c r="F58" s="56" t="n"/>
-      <c r="G58" s="56" t="n"/>
-      <c r="H58" s="57" t="n"/>
-      <c r="I58" s="58" t="n"/>
-      <c r="J58" s="56" t="n"/>
-      <c r="K58" s="56" t="n"/>
-      <c r="L58" s="57" t="n"/>
-      <c r="M58" s="58" t="n"/>
-      <c r="N58" s="56" t="n"/>
-      <c r="O58" s="56" t="n"/>
-      <c r="P58" s="57" t="n"/>
-      <c r="Q58" s="58" t="n"/>
-      <c r="R58" s="56" t="n"/>
-      <c r="S58" s="56" t="n"/>
-      <c r="T58" s="56" t="n"/>
-      <c r="U58" s="57" t="n"/>
-      <c r="V58" s="58" t="n"/>
-      <c r="W58" s="56" t="n"/>
-      <c r="X58" s="103" t="n"/>
-      <c r="Y58" s="104" t="n"/>
-      <c r="Z58" s="102" t="n"/>
-      <c r="AA58" s="104" t="n"/>
+      <c r="D58" s="58" t="n"/>
+      <c r="E58" s="56" t="n"/>
+      <c r="F58" s="55" t="n"/>
+      <c r="G58" s="55" t="n"/>
+      <c r="H58" s="64" t="n"/>
+      <c r="I58" s="54" t="n"/>
+      <c r="J58" s="55" t="n"/>
+      <c r="K58" s="55" t="n"/>
+      <c r="L58" s="64" t="n"/>
+      <c r="M58" s="54" t="n"/>
+      <c r="N58" s="55" t="n"/>
+      <c r="O58" s="55" t="n"/>
+      <c r="P58" s="64" t="n"/>
+      <c r="Q58" s="54" t="n"/>
+      <c r="R58" s="55" t="n"/>
+      <c r="S58" s="55" t="n"/>
+      <c r="T58" s="55" t="n"/>
+      <c r="U58" s="64" t="n"/>
+      <c r="V58" s="54" t="n"/>
+      <c r="W58" s="55" t="n"/>
+      <c r="X58" s="55" t="n"/>
+      <c r="Y58" s="57" t="n"/>
+      <c r="Z58" s="58" t="n"/>
+      <c r="AA58" s="57" t="n"/>
       <c r="AB58" s="59" t="n"/>
       <c r="AC58" s="60" t="n"/>
     </row>
@@ -3611,30 +3612,30 @@
           <t>설계</t>
         </is>
       </c>
-      <c r="D60" s="105" t="n"/>
-      <c r="E60" s="106" t="n"/>
-      <c r="F60" s="106" t="n"/>
-      <c r="G60" s="106" t="n"/>
-      <c r="H60" s="18" t="n"/>
-      <c r="I60" s="21" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="106" t="n"/>
-      <c r="L60" s="107" t="n"/>
-      <c r="M60" s="105" t="n"/>
-      <c r="N60" s="106" t="n"/>
-      <c r="O60" s="106" t="n"/>
-      <c r="P60" s="107" t="n"/>
-      <c r="Q60" s="105" t="n"/>
-      <c r="R60" s="106" t="n"/>
-      <c r="S60" s="106" t="n"/>
-      <c r="T60" s="106" t="n"/>
-      <c r="U60" s="107" t="n"/>
-      <c r="V60" s="105" t="n"/>
-      <c r="W60" s="106" t="n"/>
-      <c r="X60" s="106" t="n"/>
-      <c r="Y60" s="107" t="n"/>
-      <c r="Z60" s="105" t="n"/>
-      <c r="AA60" s="107" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="66" t="n"/>
+      <c r="I60" s="67" t="n"/>
+      <c r="J60" s="65" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="18" t="n"/>
+      <c r="M60" s="21" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="18" t="n"/>
+      <c r="Q60" s="21" t="n"/>
+      <c r="R60" s="5" t="n"/>
+      <c r="S60" s="5" t="n"/>
+      <c r="T60" s="5" t="n"/>
+      <c r="U60" s="18" t="n"/>
+      <c r="V60" s="21" t="n"/>
+      <c r="W60" s="5" t="n"/>
+      <c r="X60" s="5" t="n"/>
+      <c r="Y60" s="18" t="n"/>
+      <c r="Z60" s="21" t="n"/>
+      <c r="AA60" s="18" t="n"/>
       <c r="AB60" s="34" t="inlineStr">
         <is>
           <t>화면/기능 설계 검토 및 승인</t>
@@ -3654,30 +3655,30 @@
           <t>개발</t>
         </is>
       </c>
-      <c r="D61" s="105" t="n"/>
-      <c r="E61" s="106" t="n"/>
-      <c r="F61" s="106" t="n"/>
-      <c r="G61" s="106" t="n"/>
-      <c r="H61" s="107" t="n"/>
-      <c r="I61" s="105" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="n"/>
-      <c r="L61" s="18" t="n"/>
-      <c r="M61" s="21" t="n"/>
-      <c r="N61" s="5" t="n"/>
-      <c r="O61" s="5" t="n"/>
-      <c r="P61" s="18" t="n"/>
-      <c r="Q61" s="21" t="n"/>
-      <c r="R61" s="5" t="n"/>
-      <c r="S61" s="5" t="n"/>
-      <c r="T61" s="5" t="n"/>
-      <c r="U61" s="18" t="n"/>
-      <c r="V61" s="105" t="n"/>
-      <c r="W61" s="106" t="n"/>
-      <c r="X61" s="106" t="n"/>
-      <c r="Y61" s="107" t="n"/>
-      <c r="Z61" s="105" t="n"/>
-      <c r="AA61" s="107" t="n"/>
+      <c r="D61" s="21" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="18" t="n"/>
+      <c r="I61" s="21" t="n"/>
+      <c r="J61" s="65" t="n"/>
+      <c r="K61" s="65" t="n"/>
+      <c r="L61" s="66" t="n"/>
+      <c r="M61" s="67" t="n"/>
+      <c r="N61" s="65" t="n"/>
+      <c r="O61" s="65" t="n"/>
+      <c r="P61" s="66" t="n"/>
+      <c r="Q61" s="67" t="n"/>
+      <c r="R61" s="65" t="n"/>
+      <c r="S61" s="65" t="n"/>
+      <c r="T61" s="65" t="n"/>
+      <c r="U61" s="66" t="n"/>
+      <c r="V61" s="21" t="n"/>
+      <c r="W61" s="5" t="n"/>
+      <c r="X61" s="5" t="n"/>
+      <c r="Y61" s="18" t="n"/>
+      <c r="Z61" s="21" t="n"/>
+      <c r="AA61" s="18" t="n"/>
       <c r="AB61" s="34" t="inlineStr">
         <is>
           <t>개발 중간 산출물 확인</t>
@@ -3690,37 +3691,37 @@
       </c>
     </row>
     <row r="62" ht="19.95" customHeight="1" thickBot="1">
-      <c r="A62" s="101" t="n"/>
+      <c r="A62" s="80" t="n"/>
       <c r="B62" s="61" t="n"/>
       <c r="C62" s="62" t="inlineStr">
         <is>
           <t>리뷰 및 테스트</t>
         </is>
       </c>
-      <c r="D62" s="108" t="n"/>
-      <c r="E62" s="109" t="n"/>
-      <c r="F62" s="109" t="n"/>
-      <c r="G62" s="109" t="n"/>
-      <c r="H62" s="110" t="n"/>
-      <c r="I62" s="108" t="n"/>
-      <c r="J62" s="109" t="n"/>
-      <c r="K62" s="109" t="n"/>
-      <c r="L62" s="110" t="n"/>
-      <c r="M62" s="108" t="n"/>
-      <c r="N62" s="109" t="n"/>
-      <c r="O62" s="109" t="n"/>
-      <c r="P62" s="110" t="n"/>
-      <c r="Q62" s="108" t="n"/>
-      <c r="R62" s="109" t="n"/>
-      <c r="S62" s="109" t="n"/>
-      <c r="T62" s="26" t="n"/>
-      <c r="U62" s="27" t="n"/>
-      <c r="V62" s="25" t="n"/>
-      <c r="W62" s="26" t="n"/>
-      <c r="X62" s="109" t="n"/>
-      <c r="Y62" s="110" t="n"/>
-      <c r="Z62" s="108" t="n"/>
-      <c r="AA62" s="110" t="n"/>
+      <c r="D62" s="25" t="n"/>
+      <c r="E62" s="26" t="n"/>
+      <c r="F62" s="26" t="n"/>
+      <c r="G62" s="26" t="n"/>
+      <c r="H62" s="27" t="n"/>
+      <c r="I62" s="25" t="n"/>
+      <c r="J62" s="26" t="n"/>
+      <c r="K62" s="26" t="n"/>
+      <c r="L62" s="27" t="n"/>
+      <c r="M62" s="25" t="n"/>
+      <c r="N62" s="26" t="n"/>
+      <c r="O62" s="26" t="n"/>
+      <c r="P62" s="27" t="n"/>
+      <c r="Q62" s="25" t="n"/>
+      <c r="R62" s="26" t="n"/>
+      <c r="S62" s="26" t="n"/>
+      <c r="T62" s="68" t="n"/>
+      <c r="U62" s="69" t="n"/>
+      <c r="V62" s="114" t="n"/>
+      <c r="W62" s="68" t="n"/>
+      <c r="X62" s="26" t="n"/>
+      <c r="Y62" s="27" t="n"/>
+      <c r="Z62" s="25" t="n"/>
+      <c r="AA62" s="27" t="n"/>
       <c r="AB62" s="36" t="inlineStr">
         <is>
           <t>통합테스트 참여 및 결과 확인</t>
@@ -3732,246 +3733,250 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="22.05" customHeight="1">
-      <c r="A63" s="79" t="inlineStr">
+    <row r="63" ht="19.95" customHeight="1">
+      <c r="A63" s="101" t="n"/>
+      <c r="B63" s="61" t="n"/>
+      <c r="C63" s="62" t="inlineStr">
+        <is>
+          <t>검수</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="n"/>
+      <c r="E63" s="26" t="n"/>
+      <c r="F63" s="26" t="n"/>
+      <c r="G63" s="26" t="n"/>
+      <c r="H63" s="27" t="n"/>
+      <c r="I63" s="25" t="n"/>
+      <c r="J63" s="26" t="n"/>
+      <c r="K63" s="26" t="n"/>
+      <c r="L63" s="27" t="n"/>
+      <c r="M63" s="25" t="n"/>
+      <c r="N63" s="26" t="n"/>
+      <c r="O63" s="26" t="n"/>
+      <c r="P63" s="27" t="n"/>
+      <c r="Q63" s="25" t="n"/>
+      <c r="R63" s="26" t="n"/>
+      <c r="S63" s="26" t="n"/>
+      <c r="T63" s="26" t="n"/>
+      <c r="U63" s="27" t="n"/>
+      <c r="V63" s="25" t="n"/>
+      <c r="W63" s="26" t="n"/>
+      <c r="X63" s="68" t="n"/>
+      <c r="Y63" s="27" t="n"/>
+      <c r="Z63" s="25" t="n"/>
+      <c r="AA63" s="27" t="n"/>
+      <c r="AB63" s="36" t="inlineStr">
+        <is>
+          <t>검수확인서 날인</t>
+        </is>
+      </c>
+      <c r="AC63" s="37" t="inlineStr">
+        <is>
+          <t>12.21~12.24 / 추가개발 검수</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22.05" customHeight="1">
+      <c r="A64" s="79" t="inlineStr">
         <is>
           <t>시스템 검수</t>
         </is>
       </c>
-      <c r="B63" s="52" t="inlineStr">
+      <c r="B64" s="52" t="inlineStr">
         <is>
           <t>검수준비</t>
         </is>
       </c>
-      <c r="C63" s="53" t="n"/>
-      <c r="D63" s="102" t="n"/>
-      <c r="E63" s="103" t="n"/>
-      <c r="F63" s="103" t="n"/>
-      <c r="G63" s="103" t="n"/>
-      <c r="H63" s="104" t="n"/>
-      <c r="I63" s="102" t="n"/>
-      <c r="J63" s="103" t="n"/>
-      <c r="K63" s="103" t="n"/>
-      <c r="L63" s="104" t="n"/>
-      <c r="M63" s="102" t="n"/>
-      <c r="N63" s="103" t="n"/>
-      <c r="O63" s="103" t="n"/>
-      <c r="P63" s="104" t="n"/>
-      <c r="Q63" s="102" t="n"/>
-      <c r="R63" s="103" t="n"/>
-      <c r="S63" s="103" t="n"/>
-      <c r="T63" s="103" t="n"/>
-      <c r="U63" s="104" t="n"/>
-      <c r="V63" s="102" t="n"/>
-      <c r="W63" s="103" t="n"/>
-      <c r="X63" s="56" t="n"/>
-      <c r="Y63" s="104" t="n"/>
-      <c r="Z63" s="102" t="n"/>
-      <c r="AA63" s="104" t="n"/>
-      <c r="AB63" s="59" t="n"/>
-      <c r="AC63" s="60" t="n"/>
-    </row>
-    <row r="64" ht="19.95" customHeight="1">
-      <c r="A64" s="80" t="n"/>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="31" t="inlineStr">
-        <is>
-          <t>검수 시나리오 작성</t>
-        </is>
-      </c>
-      <c r="D64" s="105" t="n"/>
-      <c r="E64" s="106" t="n"/>
-      <c r="F64" s="106" t="n"/>
-      <c r="G64" s="106" t="n"/>
-      <c r="H64" s="107" t="n"/>
-      <c r="I64" s="105" t="n"/>
-      <c r="J64" s="106" t="n"/>
-      <c r="K64" s="106" t="n"/>
-      <c r="L64" s="107" t="n"/>
-      <c r="M64" s="105" t="n"/>
-      <c r="N64" s="106" t="n"/>
-      <c r="O64" s="106" t="n"/>
-      <c r="P64" s="107" t="n"/>
-      <c r="Q64" s="105" t="n"/>
-      <c r="R64" s="106" t="n"/>
-      <c r="S64" s="106" t="n"/>
-      <c r="T64" s="106" t="n"/>
-      <c r="U64" s="107" t="n"/>
-      <c r="V64" s="105" t="n"/>
-      <c r="W64" s="106" t="n"/>
-      <c r="X64" s="5" t="n"/>
-      <c r="Y64" s="107" t="n"/>
-      <c r="Z64" s="105" t="n"/>
-      <c r="AA64" s="107" t="n"/>
-      <c r="AB64" s="34" t="n"/>
-      <c r="AC64" s="35" t="n"/>
+      <c r="C64" s="53" t="n"/>
+      <c r="D64" s="58" t="n"/>
+      <c r="E64" s="56" t="n"/>
+      <c r="F64" s="56" t="n"/>
+      <c r="G64" s="56" t="n"/>
+      <c r="H64" s="57" t="n"/>
+      <c r="I64" s="58" t="n"/>
+      <c r="J64" s="56" t="n"/>
+      <c r="K64" s="56" t="n"/>
+      <c r="L64" s="57" t="n"/>
+      <c r="M64" s="58" t="n"/>
+      <c r="N64" s="56" t="n"/>
+      <c r="O64" s="56" t="n"/>
+      <c r="P64" s="57" t="n"/>
+      <c r="Q64" s="58" t="n"/>
+      <c r="R64" s="56" t="n"/>
+      <c r="S64" s="56" t="n"/>
+      <c r="T64" s="56" t="n"/>
+      <c r="U64" s="57" t="n"/>
+      <c r="V64" s="58" t="n"/>
+      <c r="W64" s="55" t="n"/>
+      <c r="X64" s="55" t="n"/>
+      <c r="Y64" s="64" t="n"/>
+      <c r="Z64" s="58" t="n"/>
+      <c r="AA64" s="57" t="n"/>
+      <c r="AB64" s="59" t="n"/>
+      <c r="AC64" s="60" t="n"/>
     </row>
     <row r="65" ht="19.95" customHeight="1">
       <c r="A65" s="80" t="n"/>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="31" t="inlineStr">
         <is>
+          <t>검수 시나리오 작성</t>
+        </is>
+      </c>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="18" t="n"/>
+      <c r="I65" s="21" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="18" t="n"/>
+      <c r="M65" s="21" t="n"/>
+      <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="18" t="n"/>
+      <c r="Q65" s="21" t="n"/>
+      <c r="R65" s="5" t="n"/>
+      <c r="S65" s="5" t="n"/>
+      <c r="T65" s="5" t="n"/>
+      <c r="U65" s="18" t="n"/>
+      <c r="V65" s="21" t="n"/>
+      <c r="W65" s="7" t="n"/>
+      <c r="X65" s="7" t="n"/>
+      <c r="Y65" s="18" t="n"/>
+      <c r="Z65" s="21" t="n"/>
+      <c r="AA65" s="18" t="n"/>
+      <c r="AB65" s="34" t="n"/>
+      <c r="AC65" s="35" t="n"/>
+    </row>
+    <row r="66" ht="19.95" customHeight="1">
+      <c r="A66" s="80" t="n"/>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="31" t="inlineStr">
+        <is>
           <t>모듈별 검수 진행</t>
         </is>
       </c>
-      <c r="D65" s="105" t="n"/>
-      <c r="E65" s="106" t="n"/>
-      <c r="F65" s="106" t="n"/>
-      <c r="G65" s="106" t="n"/>
-      <c r="H65" s="107" t="n"/>
-      <c r="I65" s="105" t="n"/>
-      <c r="J65" s="106" t="n"/>
-      <c r="K65" s="106" t="n"/>
-      <c r="L65" s="107" t="n"/>
-      <c r="M65" s="105" t="n"/>
-      <c r="N65" s="106" t="n"/>
-      <c r="O65" s="106" t="n"/>
-      <c r="P65" s="107" t="n"/>
-      <c r="Q65" s="105" t="n"/>
-      <c r="R65" s="106" t="n"/>
-      <c r="S65" s="106" t="n"/>
-      <c r="T65" s="106" t="n"/>
-      <c r="U65" s="107" t="n"/>
-      <c r="V65" s="105" t="n"/>
-      <c r="W65" s="106" t="n"/>
-      <c r="X65" s="5" t="n"/>
-      <c r="Y65" s="107" t="n"/>
-      <c r="Z65" s="105" t="n"/>
-      <c r="AA65" s="107" t="n"/>
-      <c r="AB65" s="34" t="inlineStr">
+      <c r="D66" s="21" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="18" t="n"/>
+      <c r="I66" s="21" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="18" t="n"/>
+      <c r="M66" s="21" t="n"/>
+      <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="18" t="n"/>
+      <c r="Q66" s="21" t="n"/>
+      <c r="R66" s="5" t="n"/>
+      <c r="S66" s="5" t="n"/>
+      <c r="T66" s="5" t="n"/>
+      <c r="U66" s="18" t="n"/>
+      <c r="V66" s="21" t="n"/>
+      <c r="W66" s="5" t="n"/>
+      <c r="X66" s="7" t="n"/>
+      <c r="Y66" s="23" t="n"/>
+      <c r="Z66" s="21" t="n"/>
+      <c r="AA66" s="18" t="n"/>
+      <c r="AB66" s="34" t="inlineStr">
         <is>
           <t>고객사 직접 수행</t>
         </is>
       </c>
-      <c r="AC65" s="35" t="n"/>
-    </row>
-    <row r="66" ht="19.95" customHeight="1">
-      <c r="A66" s="101" t="n"/>
-      <c r="B66" s="71" t="n"/>
-      <c r="C66" s="72" t="inlineStr">
+      <c r="AC66" s="35" t="n"/>
+    </row>
+    <row r="67" ht="19.95" customHeight="1">
+      <c r="A67" s="101" t="n"/>
+      <c r="B67" s="71" t="n"/>
+      <c r="C67" s="72" t="inlineStr">
         <is>
           <t>검수 확인</t>
         </is>
       </c>
-      <c r="D66" s="111" t="n"/>
-      <c r="E66" s="112" t="n"/>
-      <c r="F66" s="112" t="n"/>
-      <c r="G66" s="112" t="n"/>
-      <c r="H66" s="113" t="n"/>
-      <c r="I66" s="111" t="n"/>
-      <c r="J66" s="112" t="n"/>
-      <c r="K66" s="112" t="n"/>
-      <c r="L66" s="113" t="n"/>
-      <c r="M66" s="111" t="n"/>
-      <c r="N66" s="112" t="n"/>
-      <c r="O66" s="112" t="n"/>
-      <c r="P66" s="113" t="n"/>
-      <c r="Q66" s="111" t="n"/>
-      <c r="R66" s="112" t="n"/>
-      <c r="S66" s="112" t="n"/>
-      <c r="T66" s="112" t="n"/>
-      <c r="U66" s="113" t="n"/>
-      <c r="V66" s="111" t="n"/>
-      <c r="W66" s="112" t="n"/>
-      <c r="X66" s="74" t="n"/>
-      <c r="Y66" s="113" t="n"/>
-      <c r="Z66" s="111" t="n"/>
-      <c r="AA66" s="113" t="n"/>
-      <c r="AB66" s="77" t="inlineStr">
+      <c r="D67" s="73" t="n"/>
+      <c r="E67" s="74" t="n"/>
+      <c r="F67" s="74" t="n"/>
+      <c r="G67" s="74" t="n"/>
+      <c r="H67" s="75" t="n"/>
+      <c r="I67" s="73" t="n"/>
+      <c r="J67" s="74" t="n"/>
+      <c r="K67" s="74" t="n"/>
+      <c r="L67" s="75" t="n"/>
+      <c r="M67" s="73" t="n"/>
+      <c r="N67" s="74" t="n"/>
+      <c r="O67" s="74" t="n"/>
+      <c r="P67" s="75" t="n"/>
+      <c r="Q67" s="73" t="n"/>
+      <c r="R67" s="74" t="n"/>
+      <c r="S67" s="74" t="n"/>
+      <c r="T67" s="74" t="n"/>
+      <c r="U67" s="75" t="n"/>
+      <c r="V67" s="73" t="n"/>
+      <c r="W67" s="74" t="n"/>
+      <c r="X67" s="74" t="n"/>
+      <c r="Y67" s="76" t="n"/>
+      <c r="Z67" s="73" t="n"/>
+      <c r="AA67" s="75" t="n"/>
+      <c r="AB67" s="77" t="inlineStr">
         <is>
           <t>검수확인서 날인</t>
         </is>
       </c>
-      <c r="AC66" s="78" t="n"/>
-    </row>
-    <row r="67" ht="22.05" customHeight="1">
-      <c r="A67" s="82" t="inlineStr">
+      <c r="AC67" s="78" t="n"/>
+    </row>
+    <row r="68" ht="22.05" customHeight="1">
+      <c r="A68" s="82" t="inlineStr">
         <is>
           <t>시스템 오픈</t>
         </is>
       </c>
-      <c r="B67" s="40" t="inlineStr">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t>오픈 준비</t>
         </is>
       </c>
-      <c r="C67" s="41" t="n"/>
-      <c r="D67" s="45" t="n"/>
-      <c r="E67" s="43" t="n"/>
-      <c r="F67" s="43" t="n"/>
-      <c r="G67" s="43" t="n"/>
-      <c r="H67" s="44" t="n"/>
-      <c r="I67" s="45" t="n"/>
-      <c r="J67" s="43" t="n"/>
-      <c r="K67" s="43" t="n"/>
-      <c r="L67" s="44" t="n"/>
-      <c r="M67" s="45" t="n"/>
-      <c r="N67" s="43" t="n"/>
-      <c r="O67" s="43" t="n"/>
-      <c r="P67" s="44" t="n"/>
-      <c r="Q67" s="45" t="n"/>
-      <c r="R67" s="43" t="n"/>
-      <c r="S67" s="43" t="n"/>
-      <c r="T67" s="43" t="n"/>
-      <c r="U67" s="44" t="n"/>
-      <c r="V67" s="45" t="n"/>
-      <c r="W67" s="43" t="n"/>
-      <c r="X67" s="43" t="n"/>
-      <c r="Y67" s="51" t="n"/>
-      <c r="Z67" s="42" t="n"/>
-      <c r="AA67" s="44" t="n"/>
-      <c r="AB67" s="46" t="inlineStr">
+      <c r="C68" s="41" t="n"/>
+      <c r="D68" s="45" t="n"/>
+      <c r="E68" s="43" t="n"/>
+      <c r="F68" s="43" t="n"/>
+      <c r="G68" s="43" t="n"/>
+      <c r="H68" s="44" t="n"/>
+      <c r="I68" s="45" t="n"/>
+      <c r="J68" s="43" t="n"/>
+      <c r="K68" s="43" t="n"/>
+      <c r="L68" s="44" t="n"/>
+      <c r="M68" s="45" t="n"/>
+      <c r="N68" s="43" t="n"/>
+      <c r="O68" s="43" t="n"/>
+      <c r="P68" s="44" t="n"/>
+      <c r="Q68" s="45" t="n"/>
+      <c r="R68" s="43" t="n"/>
+      <c r="S68" s="43" t="n"/>
+      <c r="T68" s="43" t="n"/>
+      <c r="U68" s="44" t="n"/>
+      <c r="V68" s="45" t="n"/>
+      <c r="W68" s="43" t="n"/>
+      <c r="X68" s="43" t="n"/>
+      <c r="Y68" s="51" t="n"/>
+      <c r="Z68" s="42" t="n"/>
+      <c r="AA68" s="44" t="n"/>
+      <c r="AB68" s="46" t="inlineStr">
         <is>
           <t>인사부서 등 프리오픈(권장): 전사 오픈 전에도 인사팀 데이터는 계속 축적 필요</t>
         </is>
       </c>
-      <c r="AC67" s="47" t="n"/>
-    </row>
-    <row r="68" ht="19.95" customHeight="1">
-      <c r="A68" s="80" t="n"/>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="31" t="inlineStr">
-        <is>
-          <t>인사시스템 데이터 및 기준설정 최종점검</t>
-        </is>
-      </c>
-      <c r="D68" s="21" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="18" t="n"/>
-      <c r="I68" s="21" t="n"/>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="n"/>
-      <c r="L68" s="18" t="n"/>
-      <c r="M68" s="21" t="n"/>
-      <c r="N68" s="5" t="n"/>
-      <c r="O68" s="5" t="n"/>
-      <c r="P68" s="18" t="n"/>
-      <c r="Q68" s="21" t="n"/>
-      <c r="R68" s="5" t="n"/>
-      <c r="S68" s="5" t="n"/>
-      <c r="T68" s="5" t="n"/>
-      <c r="U68" s="18" t="n"/>
-      <c r="V68" s="21" t="n"/>
-      <c r="W68" s="5" t="n"/>
-      <c r="X68" s="5" t="n"/>
-      <c r="Y68" s="23" t="n"/>
-      <c r="Z68" s="19" t="n"/>
-      <c r="AA68" s="18" t="n"/>
-      <c r="AB68" s="34" t="inlineStr">
-        <is>
-          <t>임직원용 매뉴얼/교육 준비</t>
-        </is>
-      </c>
-      <c r="AC68" s="35" t="n"/>
+      <c r="AC68" s="47" t="n"/>
     </row>
     <row r="69" ht="19.95" customHeight="1">
       <c r="A69" s="80" t="n"/>
       <c r="B69" s="6" t="n"/>
       <c r="C69" s="31" t="inlineStr">
         <is>
-          <t>추가개발 및 최종점검</t>
+          <t>인사시스템 데이터 및 기준설정 최종점검</t>
         </is>
       </c>
       <c r="D69" s="21" t="n"/>
@@ -3995,20 +4000,24 @@
       <c r="V69" s="21" t="n"/>
       <c r="W69" s="5" t="n"/>
       <c r="X69" s="5" t="n"/>
-      <c r="Y69" s="66" t="n"/>
-      <c r="Z69" s="67" t="n"/>
+      <c r="Y69" s="23" t="n"/>
+      <c r="Z69" s="19" t="n"/>
       <c r="AA69" s="18" t="n"/>
-      <c r="AB69" s="34" t="n"/>
+      <c r="AB69" s="34" t="inlineStr">
+        <is>
+          <t>임직원용 매뉴얼/교육 준비</t>
+        </is>
+      </c>
       <c r="AC69" s="35" t="n"/>
     </row>
-    <row r="70" ht="22.05" customHeight="1">
+    <row r="70" ht="19.95" customHeight="1">
       <c r="A70" s="80" t="n"/>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>인사시스템 오픈</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="n"/>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="31" t="inlineStr">
+        <is>
+          <t>추가개발 및 최종점검</t>
+        </is>
+      </c>
       <c r="D70" s="21" t="n"/>
       <c r="E70" s="5" t="n"/>
       <c r="F70" s="5" t="n"/>
@@ -4030,79 +4039,114 @@
       <c r="V70" s="21" t="n"/>
       <c r="W70" s="5" t="n"/>
       <c r="X70" s="5" t="n"/>
-      <c r="Y70" s="18" t="n"/>
-      <c r="Z70" s="17" t="n"/>
+      <c r="Y70" s="66" t="n"/>
+      <c r="Z70" s="67" t="n"/>
       <c r="AA70" s="18" t="n"/>
       <c r="AB70" s="34" t="n"/>
-      <c r="AC70" s="39" t="inlineStr">
+      <c r="AC70" s="35" t="n"/>
+    </row>
+    <row r="71" ht="22.05" customHeight="1" thickBot="1">
+      <c r="A71" s="80" t="n"/>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>인사시스템 오픈</t>
+        </is>
+      </c>
+      <c r="C71" s="30" t="n"/>
+      <c r="D71" s="21" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="18" t="n"/>
+      <c r="I71" s="21" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="18" t="n"/>
+      <c r="M71" s="21" t="n"/>
+      <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="18" t="n"/>
+      <c r="Q71" s="21" t="n"/>
+      <c r="R71" s="5" t="n"/>
+      <c r="S71" s="5" t="n"/>
+      <c r="T71" s="5" t="n"/>
+      <c r="U71" s="18" t="n"/>
+      <c r="V71" s="21" t="n"/>
+      <c r="W71" s="5" t="n"/>
+      <c r="X71" s="5" t="n"/>
+      <c r="Y71" s="18" t="n"/>
+      <c r="Z71" s="17" t="n"/>
+      <c r="AA71" s="18" t="n"/>
+      <c r="AB71" s="34" t="n"/>
+      <c r="AC71" s="39" t="inlineStr">
         <is>
           <t>2027.01.04 오픈</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="22.05" customHeight="1" thickBot="1">
-      <c r="A71" s="101" t="n"/>
-      <c r="B71" s="32" t="inlineStr">
+    <row r="72" ht="22.05" customHeight="1">
+      <c r="A72" s="101" t="n"/>
+      <c r="B72" s="32" t="inlineStr">
         <is>
           <t>인사시스템 안정화 지원</t>
         </is>
       </c>
-      <c r="C71" s="33" t="n"/>
-      <c r="D71" s="25" t="n"/>
-      <c r="E71" s="26" t="n"/>
-      <c r="F71" s="26" t="n"/>
-      <c r="G71" s="26" t="n"/>
-      <c r="H71" s="27" t="n"/>
-      <c r="I71" s="25" t="n"/>
-      <c r="J71" s="26" t="n"/>
-      <c r="K71" s="26" t="n"/>
-      <c r="L71" s="27" t="n"/>
-      <c r="M71" s="25" t="n"/>
-      <c r="N71" s="26" t="n"/>
-      <c r="O71" s="26" t="n"/>
-      <c r="P71" s="27" t="n"/>
-      <c r="Q71" s="25" t="n"/>
-      <c r="R71" s="26" t="n"/>
-      <c r="S71" s="26" t="n"/>
-      <c r="T71" s="26" t="n"/>
-      <c r="U71" s="27" t="n"/>
-      <c r="V71" s="25" t="n"/>
-      <c r="W71" s="26" t="n"/>
-      <c r="X71" s="26" t="n"/>
-      <c r="Y71" s="27" t="n"/>
-      <c r="Z71" s="28" t="n"/>
-      <c r="AA71" s="29" t="n"/>
-      <c r="AB71" s="36" t="n"/>
-      <c r="AC71" s="37" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="C72" s="33" t="n"/>
+      <c r="D72" s="25" t="n"/>
+      <c r="E72" s="26" t="n"/>
+      <c r="F72" s="26" t="n"/>
+      <c r="G72" s="26" t="n"/>
+      <c r="H72" s="27" t="n"/>
+      <c r="I72" s="25" t="n"/>
+      <c r="J72" s="26" t="n"/>
+      <c r="K72" s="26" t="n"/>
+      <c r="L72" s="27" t="n"/>
+      <c r="M72" s="25" t="n"/>
+      <c r="N72" s="26" t="n"/>
+      <c r="O72" s="26" t="n"/>
+      <c r="P72" s="27" t="n"/>
+      <c r="Q72" s="25" t="n"/>
+      <c r="R72" s="26" t="n"/>
+      <c r="S72" s="26" t="n"/>
+      <c r="T72" s="26" t="n"/>
+      <c r="U72" s="27" t="n"/>
+      <c r="V72" s="25" t="n"/>
+      <c r="W72" s="26" t="n"/>
+      <c r="X72" s="26" t="n"/>
+      <c r="Y72" s="27" t="n"/>
+      <c r="Z72" s="28" t="n"/>
+      <c r="AA72" s="29" t="n"/>
+      <c r="AB72" s="36" t="n"/>
+      <c r="AC72" s="37" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>* 상기 일정은 사업 수행과정의 상황에 따라 변경될 수 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="9" t="n"/>
+    <row r="75">
+      <c r="A75" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="M9:P9"/>
     <mergeCell ref="A2:AB2"/>
-    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="A58:A63"/>
+    <mergeCell ref="A68:A72"/>
     <mergeCell ref="V9:Y9"/>
     <mergeCell ref="I9:L9"/>
+    <mergeCell ref="A12:A18"/>
     <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="A12:A18"/>
     <mergeCell ref="AC9:AC11"/>
     <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A64:A67"/>
     <mergeCell ref="A19:A57"/>
     <mergeCell ref="Q9:U9"/>
-    <mergeCell ref="A63:A66"/>
     <mergeCell ref="Z9:AA9"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="D9:H9"/>
-    <mergeCell ref="A58:A62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
